--- a/data/sars/pacific/tables/Pacific_2014_Appendix3.xlsx
+++ b/data/sars/pacific/tables/Pacific_2014_Appendix3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/pacific/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E4526F-56A6-764B-AA13-63547B6A6EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B74195-30D0-F84D-AE68-0D8995DD25CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="500" windowWidth="29880" windowHeight="20180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="124">
   <si>
     <t>California sea lion</t>
   </si>
@@ -355,9 +355,6 @@
     <t>survey3</t>
   </si>
   <si>
-    <t>revised</t>
-  </si>
-  <si>
     <t>pbr</t>
   </si>
   <si>
@@ -377,6 +374,24 @@
   </si>
   <si>
     <t>rf</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>RF=0.2 in SAR; RF=0.1 was typo in table</t>
+  </si>
+  <si>
+    <t>RF=0.5 in SAR; RF=0.4 was typo in table</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>revision_yr</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -818,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q87"/>
+  <dimension ref="A1:R87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="31.3984375" style="1" bestFit="1" customWidth="1"/>
@@ -833,12 +848,13 @@
     <col min="11" max="11" width="14.19921875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="15" width="9.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.59765625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="29.796875" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="1"/>
+    <col min="16" max="16" width="13.19921875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="15.19921875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="43.3984375" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" ht="30" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>100</v>
       </c>
@@ -861,16 +877,16 @@
         <v>106</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I1" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="L1" s="8" t="s">
         <v>107</v>
@@ -885,11 +901,16 @@
         <v>110</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q1" s="8"/>
-    </row>
-    <row r="2" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+        <v>122</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -938,9 +959,12 @@
       <c r="P2" s="11">
         <v>2014</v>
       </c>
-      <c r="Q2" s="3"/>
-    </row>
-    <row r="3" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q2" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="R2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -989,9 +1013,12 @@
       <c r="P3" s="11">
         <v>2014</v>
       </c>
-      <c r="Q3" s="3"/>
-    </row>
-    <row r="4" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q3" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="R3" s="3"/>
+    </row>
+    <row r="4" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -1036,9 +1063,10 @@
       <c r="P4" s="13">
         <v>2013</v>
       </c>
-      <c r="Q4" s="3"/>
-    </row>
-    <row r="5" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q4" s="13"/>
+      <c r="R4" s="3"/>
+    </row>
+    <row r="5" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
@@ -1083,9 +1111,10 @@
       <c r="P5" s="13">
         <v>2013</v>
       </c>
-      <c r="Q5" s="3"/>
-    </row>
-    <row r="6" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q5" s="13"/>
+      <c r="R5" s="3"/>
+    </row>
+    <row r="6" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
@@ -1130,9 +1159,10 @@
       <c r="P6" s="13">
         <v>2013</v>
       </c>
-      <c r="Q6" s="3"/>
-    </row>
-    <row r="7" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q6" s="13"/>
+      <c r="R6" s="3"/>
+    </row>
+    <row r="7" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
@@ -1177,9 +1207,10 @@
       <c r="P7" s="13">
         <v>2013</v>
       </c>
-      <c r="Q7" s="3"/>
-    </row>
-    <row r="8" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q7" s="13"/>
+      <c r="R7" s="3"/>
+    </row>
+    <row r="8" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -1228,9 +1259,12 @@
       <c r="P8" s="11">
         <v>2014</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q8" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
@@ -1275,9 +1309,10 @@
       <c r="P9" s="13">
         <v>2000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q9" s="13"/>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
         <v>19</v>
       </c>
@@ -1326,9 +1361,10 @@
       <c r="P10" s="13">
         <v>2013</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q10" s="13"/>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -1377,9 +1413,12 @@
       <c r="P11" s="11">
         <v>2014</v>
       </c>
-      <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q11" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
         <v>25</v>
       </c>
@@ -1428,9 +1467,10 @@
       <c r="P12" s="13">
         <v>2013</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q12" s="13"/>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
         <v>25</v>
       </c>
@@ -1479,9 +1519,10 @@
       <c r="P13" s="13">
         <v>2013</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q13" s="13"/>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
         <v>25</v>
       </c>
@@ -1530,9 +1571,10 @@
       <c r="P14" s="13">
         <v>2013</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q14" s="13"/>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
         <v>25</v>
       </c>
@@ -1581,9 +1623,10 @@
       <c r="P15" s="13">
         <v>2013</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q15" s="13"/>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
         <v>25</v>
       </c>
@@ -1632,9 +1675,10 @@
       <c r="P16" s="13">
         <v>2013</v>
       </c>
-      <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q16" s="13"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
         <v>25</v>
       </c>
@@ -1683,9 +1727,10 @@
       <c r="P17" s="13">
         <v>2011</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q17" s="13"/>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
         <v>35</v>
       </c>
@@ -1734,9 +1779,10 @@
       <c r="P18" s="13">
         <v>2010</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q18" s="13"/>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A19" s="4" t="s">
         <v>38</v>
       </c>
@@ -1785,9 +1831,10 @@
       <c r="P19" s="13">
         <v>2013</v>
       </c>
-      <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q19" s="13"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A20" s="4" t="s">
         <v>39</v>
       </c>
@@ -1836,9 +1883,10 @@
       <c r="P20" s="13">
         <v>2010</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q20" s="13"/>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
         <v>40</v>
       </c>
@@ -1887,9 +1935,10 @@
       <c r="P21" s="13">
         <v>2008</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q21" s="13"/>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
         <v>40</v>
       </c>
@@ -1938,9 +1987,10 @@
       <c r="P22" s="13">
         <v>2013</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q22" s="13"/>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
         <v>44</v>
       </c>
@@ -1989,9 +2039,10 @@
       <c r="P23" s="13">
         <v>2010</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="1:17" ht="30" x14ac:dyDescent="0.15">
+      <c r="Q23" s="13"/>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="1:18" ht="30" x14ac:dyDescent="0.15">
       <c r="A24" s="4" t="s">
         <v>45</v>
       </c>
@@ -2040,9 +2091,10 @@
       <c r="P24" s="13">
         <v>2010</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q24" s="13"/>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A25" s="4" t="s">
         <v>46</v>
       </c>
@@ -2091,9 +2143,10 @@
       <c r="P25" s="13">
         <v>2012</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q25" s="13"/>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A26" s="4" t="s">
         <v>47</v>
       </c>
@@ -2142,9 +2195,10 @@
       <c r="P26" s="13">
         <v>2010</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q26" s="13"/>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="4" t="s">
         <v>48</v>
       </c>
@@ -2193,9 +2247,10 @@
       <c r="P27" s="13">
         <v>2010</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q27" s="13"/>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>48</v>
       </c>
@@ -2244,9 +2299,12 @@
       <c r="P28" s="11">
         <v>2014</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q28" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A29" s="4" t="s">
         <v>52</v>
       </c>
@@ -2269,7 +2327,7 @@
         <v>0.04</v>
       </c>
       <c r="H29" s="14">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I29" s="14">
         <v>4.5999999999999996</v>
@@ -2295,9 +2353,12 @@
       <c r="P29" s="13">
         <v>2010</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q29" s="13"/>
+      <c r="R29" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="s">
         <v>53</v>
       </c>
@@ -2346,9 +2407,10 @@
       <c r="P30" s="13">
         <v>2013</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q30" s="13"/>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A31" s="4" t="s">
         <v>54</v>
       </c>
@@ -2397,9 +2459,10 @@
       <c r="P31" s="13">
         <v>2013</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q31" s="13"/>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A32" s="4" t="s">
         <v>55</v>
       </c>
@@ -2448,9 +2511,10 @@
       <c r="P32" s="13">
         <v>2013</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q32" s="13"/>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A33" s="4" t="s">
         <v>56</v>
       </c>
@@ -2499,9 +2563,10 @@
       <c r="P33" s="13">
         <v>2010</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q33" s="13"/>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A34" s="4" t="s">
         <v>57</v>
       </c>
@@ -2550,9 +2615,10 @@
       <c r="P34" s="13">
         <v>2010</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q34" s="13"/>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
         <v>58</v>
       </c>
@@ -2601,9 +2667,12 @@
       <c r="P35" s="11">
         <v>2014</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="36" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q35" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="36" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
         <v>59</v>
       </c>
@@ -2652,9 +2721,12 @@
       <c r="P36" s="11">
         <v>2014</v>
       </c>
-      <c r="Q36" s="3"/>
-    </row>
-    <row r="37" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q36" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="R36" s="3"/>
+    </row>
+    <row r="37" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
         <v>59</v>
       </c>
@@ -2699,9 +2771,12 @@
       <c r="P37" s="11">
         <v>2014</v>
       </c>
-      <c r="Q37" s="3"/>
-    </row>
-    <row r="38" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q37" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="R37" s="3"/>
+    </row>
+    <row r="38" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A38" s="4" t="s">
         <v>62</v>
       </c>
@@ -2750,9 +2825,10 @@
       <c r="P38" s="13">
         <v>2013</v>
       </c>
-      <c r="Q38" s="3"/>
-    </row>
-    <row r="39" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q38" s="13"/>
+      <c r="R38" s="3"/>
+    </row>
+    <row r="39" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
         <v>65</v>
       </c>
@@ -2801,9 +2877,10 @@
       <c r="P39" s="13">
         <v>2013</v>
       </c>
-      <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q39" s="13"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A40" s="4" t="s">
         <v>66</v>
       </c>
@@ -2852,9 +2929,10 @@
       <c r="P40" s="13">
         <v>2013</v>
       </c>
-      <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q40" s="13"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A41" s="4" t="s">
         <v>67</v>
       </c>
@@ -2903,9 +2981,10 @@
       <c r="P41" s="13">
         <v>2010</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q41" s="13"/>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A42" s="4" t="s">
         <v>68</v>
       </c>
@@ -2954,9 +3033,10 @@
       <c r="P42" s="13">
         <v>2010</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q42" s="13"/>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
         <v>69</v>
       </c>
@@ -3003,9 +3083,10 @@
       <c r="P43" s="13">
         <v>2013</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q43" s="13"/>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A44" s="4" t="s">
         <v>69</v>
       </c>
@@ -3054,9 +3135,10 @@
       <c r="P44" s="13">
         <v>2010</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q44" s="13"/>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A45" s="4" t="s">
         <v>39</v>
       </c>
@@ -3103,9 +3185,10 @@
       <c r="P45" s="13">
         <v>2013</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q45" s="13"/>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A46" s="4" t="s">
         <v>40</v>
       </c>
@@ -3152,9 +3235,10 @@
       <c r="P46" s="13">
         <v>2013</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q46" s="13"/>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A47" s="4" t="s">
         <v>40</v>
       </c>
@@ -3203,9 +3287,10 @@
       <c r="P47" s="13">
         <v>2013</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q47" s="13"/>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A48" s="4" t="s">
         <v>40</v>
       </c>
@@ -3254,9 +3339,10 @@
       <c r="P48" s="13">
         <v>2013</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q48" s="13"/>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A49" s="4" t="s">
         <v>40</v>
       </c>
@@ -3305,9 +3391,10 @@
       <c r="P49" s="13">
         <v>2013</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q49" s="13"/>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A50" s="4" t="s">
         <v>40</v>
       </c>
@@ -3356,9 +3443,10 @@
       <c r="P50" s="13">
         <v>2013</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q50" s="13"/>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A51" s="4" t="s">
         <v>76</v>
       </c>
@@ -3405,9 +3493,10 @@
       <c r="P51" s="13">
         <v>2013</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q51" s="13"/>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A52" s="4" t="s">
         <v>76</v>
       </c>
@@ -3452,9 +3541,10 @@
       <c r="P52" s="13">
         <v>2013</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q52" s="13"/>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A53" s="4" t="s">
         <v>76</v>
       </c>
@@ -3499,9 +3589,10 @@
       <c r="P53" s="13">
         <v>2013</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q53" s="13"/>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A54" s="4" t="s">
         <v>76</v>
       </c>
@@ -3546,9 +3637,10 @@
       <c r="P54" s="13">
         <v>2013</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q54" s="13"/>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A55" s="4" t="s">
         <v>77</v>
       </c>
@@ -3595,9 +3687,10 @@
       <c r="P55" s="13">
         <v>2013</v>
       </c>
-      <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q55" s="13"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A56" s="4" t="s">
         <v>77</v>
       </c>
@@ -3646,9 +3739,10 @@
       <c r="P56" s="13">
         <v>2013</v>
       </c>
-      <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q56" s="13"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A57" s="4" t="s">
         <v>77</v>
       </c>
@@ -3697,9 +3791,10 @@
       <c r="P57" s="13">
         <v>2013</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q57" s="13"/>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A58" s="4" t="s">
         <v>77</v>
       </c>
@@ -3748,9 +3843,10 @@
       <c r="P58" s="13">
         <v>2013</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q58" s="13"/>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A59" s="4" t="s">
         <v>77</v>
       </c>
@@ -3797,9 +3893,10 @@
       <c r="P59" s="13">
         <v>2013</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q59" s="13"/>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A60" s="4" t="s">
         <v>77</v>
       </c>
@@ -3844,9 +3941,10 @@
       <c r="P60" s="13">
         <v>2013</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q60" s="13"/>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A61" s="4" t="s">
         <v>77</v>
       </c>
@@ -3891,9 +3989,10 @@
       <c r="P61" s="13">
         <v>2010</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q61" s="13"/>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A62" s="4" t="s">
         <v>44</v>
       </c>
@@ -3940,9 +4039,10 @@
       <c r="P62" s="13">
         <v>2013</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q62" s="13"/>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A63" s="4" t="s">
         <v>82</v>
       </c>
@@ -3989,9 +4089,10 @@
       <c r="P63" s="13">
         <v>2010</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q63" s="13"/>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A64" s="4" t="s">
         <v>83</v>
       </c>
@@ -4038,9 +4139,10 @@
       <c r="P64" s="13">
         <v>2013</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q64" s="13"/>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A65" s="4" t="s">
         <v>83</v>
       </c>
@@ -4085,9 +4187,10 @@
       <c r="P65" s="13">
         <v>2013</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q65" s="13"/>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A66" s="4" t="s">
         <v>86</v>
       </c>
@@ -4134,9 +4237,10 @@
       <c r="P66" s="13">
         <v>2013</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q66" s="13"/>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
         <v>87</v>
       </c>
@@ -4181,9 +4285,12 @@
       <c r="P67" s="11">
         <v>2014</v>
       </c>
-      <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q67" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
         <v>87</v>
       </c>
@@ -4230,9 +4337,12 @@
       <c r="P68" s="11">
         <v>2014</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q68" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A69" s="4" t="s">
         <v>87</v>
       </c>
@@ -4277,9 +4387,10 @@
       <c r="P69" s="13">
         <v>2013</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q69" s="13"/>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
         <v>87</v>
       </c>
@@ -4328,9 +4439,12 @@
       <c r="P70" s="11">
         <v>2014</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q70" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A71" s="4" t="s">
         <v>87</v>
       </c>
@@ -4379,9 +4493,10 @@
       <c r="P71" s="13">
         <v>2010</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q71" s="13"/>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A72" s="4" t="s">
         <v>48</v>
       </c>
@@ -4428,9 +4543,10 @@
       <c r="P72" s="13">
         <v>2013</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q72" s="13"/>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A73" s="4" t="s">
         <v>91</v>
       </c>
@@ -4477,9 +4593,10 @@
       <c r="P73" s="13">
         <v>2013</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q73" s="13"/>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A74" s="4" t="s">
         <v>92</v>
       </c>
@@ -4526,9 +4643,10 @@
       <c r="P74" s="13">
         <v>2013</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q74" s="13"/>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A75" s="4" t="s">
         <v>93</v>
       </c>
@@ -4575,9 +4693,10 @@
       <c r="P75" s="13">
         <v>2013</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q75" s="13"/>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A76" s="4" t="s">
         <v>55</v>
       </c>
@@ -4624,9 +4743,10 @@
       <c r="P76" s="13">
         <v>2013</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q76" s="13"/>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A77" s="4" t="s">
         <v>94</v>
       </c>
@@ -4673,9 +4793,10 @@
       <c r="P77" s="13">
         <v>2013</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="78" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q77" s="13"/>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="78" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A78" s="4" t="s">
         <v>57</v>
       </c>
@@ -4722,9 +4843,10 @@
       <c r="P78" s="13">
         <v>2013</v>
       </c>
-      <c r="Q78" s="3"/>
-    </row>
-    <row r="79" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q78" s="13"/>
+      <c r="R78" s="3"/>
+    </row>
+    <row r="79" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A79" s="4" t="s">
         <v>58</v>
       </c>
@@ -4747,7 +4869,7 @@
         <v>0.04</v>
       </c>
       <c r="H79" s="14">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I79" s="14">
         <v>10.199999999999999</v>
@@ -4771,9 +4893,12 @@
       <c r="P79" s="13">
         <v>2013</v>
       </c>
-      <c r="Q79" s="3"/>
-    </row>
-    <row r="80" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q79" s="13"/>
+      <c r="R79" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A80" s="4" t="s">
         <v>65</v>
       </c>
@@ -4820,9 +4945,10 @@
       <c r="P80" s="13">
         <v>2013</v>
       </c>
-      <c r="Q80" s="3"/>
-    </row>
-    <row r="81" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q80" s="13"/>
+      <c r="R80" s="3"/>
+    </row>
+    <row r="81" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A81" s="4" t="s">
         <v>66</v>
       </c>
@@ -4869,11 +4995,12 @@
       <c r="P81" s="13">
         <v>2013</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="1:17" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q81" s="13"/>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="1:18" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A82" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>21</v>
@@ -4918,9 +5045,10 @@
       <c r="P82" s="13">
         <v>2013</v>
       </c>
-      <c r="Q82" s="6"/>
-    </row>
-    <row r="83" spans="1:17" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q82" s="13"/>
+      <c r="R82" s="6"/>
+    </row>
+    <row r="83" spans="1:18" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A83" s="4" t="s">
         <v>67</v>
       </c>
@@ -4967,9 +5095,10 @@
       <c r="P83" s="13">
         <v>2013</v>
       </c>
-      <c r="Q83" s="6"/>
-    </row>
-    <row r="84" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q83" s="13"/>
+      <c r="R83" s="6"/>
+    </row>
+    <row r="84" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A84" s="4" t="s">
         <v>68</v>
       </c>
@@ -5016,9 +5145,10 @@
       <c r="P84" s="13">
         <v>2013</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q84" s="13"/>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A85" s="4" t="s">
         <v>62</v>
       </c>
@@ -5067,9 +5197,10 @@
       <c r="P85" s="13">
         <v>2009</v>
       </c>
-      <c r="Q85" s="5"/>
-    </row>
-    <row r="86" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q85" s="13"/>
+      <c r="R85" s="5"/>
+    </row>
+    <row r="86" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A86" s="4" t="s">
         <v>96</v>
       </c>
@@ -5098,10 +5229,10 @@
         <v>8</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L86" s="4" t="s">
         <v>18</v>
@@ -5118,9 +5249,10 @@
       <c r="P86" s="13">
         <v>2008</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q86" s="13"/>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A87" s="4" t="s">
         <v>96</v>
       </c>
@@ -5149,10 +5281,10 @@
         <v>11</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L87" s="4" t="s">
         <v>4</v>
@@ -5169,7 +5301,8 @@
       <c r="P87" s="13">
         <v>2008</v>
       </c>
-      <c r="Q87" s="3"/>
+      <c r="Q87" s="13"/>
+      <c r="R87" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
